--- a/naver-place-crawler/results_nail/용인_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/용인_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V219"/>
+  <dimension ref="A1:V269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20625,44 +20625,40 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>스페이스와이 SPACE Y</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>yonseiblog@naver.com</t>
-        </is>
-      </c>
+          <t>나는 너의 네일</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
-          <t>0507-1396-3851</t>
+          <t>0507-1391-8690</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로 599 303호</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 5층(다이소 바로 옆건물)</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_Jxahxkxj/friend</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -20678,39 +20674,4571 @@
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P219" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>40</v>
+      </c>
+      <c r="R219" t="n">
+        <v>49</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>1174632490</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1174632490</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>별빛네일</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>0507-1354-4095</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄시범한빛길 13-1 102호</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>http://instagram.com/starlight__nail_</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>7</v>
+      </c>
+      <c r="R220" t="n">
+        <v>245</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>1794901339</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1794901339</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>네일일번지&amp;문제성발전문</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>gksrudwls617@naver.com</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>0507-1316-2988</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 만현로 69 2층</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://naver.me/x1ePI4jg</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>197</v>
+      </c>
+      <c r="R221" t="n">
+        <v>299</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>1664651078</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1664651078</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>민네일</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>0507-1341-7492</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 반달로7번길 30 르네상스시티프라자 2층 250~258호</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Hxktqn</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>5</v>
+      </c>
+      <c r="R222" t="n">
+        <v>149</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>1400710882</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1400710882</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>블링블링</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>0502-0935-5800</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 농서로 236</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="n">
+      <c r="Q223" t="n">
         <v>0</v>
       </c>
-      <c r="R219" t="n">
+      <c r="R223" t="n">
         <v>0</v>
       </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T219" t="inlineStr">
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>1436837431</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1436837431</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>글로리네일샵</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>bluerose21c@naver.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0507-1314-5897</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 죽전로144번길 4-7 1층</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glorynail.honey</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>411</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>10</v>
+      </c>
+      <c r="R224" t="n">
+        <v>421</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>1775526503</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1775526503</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>체체네일</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0507-1486-4177</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄지성로 104</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chex2_nail/</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>411</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>411</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>1466207158</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1466207158</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>네일바이윤</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>greta0074@naver.com</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>0507-1328-3983</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 죽전로 11 606호</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_by_youn/</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>4292</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>76</v>
+      </c>
+      <c r="R226" t="n">
+        <v>4368</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>1241379622</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1241379622</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>더예쁨</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>070-4024-8990</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>경기도 광주시 능평로 195 상가동 2층 202호</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://instagram.com/thepretty_nail</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>4</v>
+      </c>
+      <c r="R227" t="n">
+        <v>42</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>1223167351</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1223167351</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>제이뷰티</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>j_beauty_lab@naver.com</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>0507-1319-1271</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 한터로 159 1층 103호</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imjeongyun187?igsh=MWh6bmZ6enV1Ynk1aA==</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>17</v>
+      </c>
+      <c r="R228" t="n">
+        <v>217</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>1883484078</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1883484078</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>네일온도</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄순환대로 400 우성스타시티 A동 2층</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.ondo_</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>10</v>
+      </c>
+      <c r="R229" t="n">
+        <v>20</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>1005241201</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1005241201</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>오늘네일</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>0507-1379-6446</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 풍덕천로 149 3층 312호</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>4</v>
+      </c>
+      <c r="R230" t="n">
+        <v>4</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>1282880424</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282880424</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>네일_유노이아</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>0507-1426-0754</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 명지로 24 용인역북더럭스나인 2층 220호</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.eunoia</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>4</v>
+      </c>
+      <c r="R231" t="n">
+        <v>124</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>1090560567</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1090560567</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>시크네일</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>0507-1396-4401</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄반송1길 20-5 1층 101호 Chic.</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chic.nail_</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>303</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>1395867499</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1395867499</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>짱유네일</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>0507-1343-9565</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 신봉1로 9</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>http://instagram.com/jjangyou_nail</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>368</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>114</v>
+      </c>
+      <c r="R233" t="n">
+        <v>482</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>1375166098</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1375166098</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>소소한네일</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 흥덕2로118번길 22 상가 102호</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailist_h.yeong</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>172</v>
+      </c>
+      <c r="R234" t="n">
+        <v>794</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>803449842</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/803449842</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>네일와썹</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>0507-1360-5662</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 동백7로 58 상가동 1층 101호</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_wassup</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>1</v>
+      </c>
+      <c r="R235" t="n">
+        <v>137</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>1236527982</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236527982</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>무드비네일 페디크루 화성동탄점 내성발톱 무좀 발각질</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>dltntbrk@naver.com</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>0507-1396-7036</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄대로6길 17 1층 105호 일부호</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dltntbrk</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>238</v>
+      </c>
+      <c r="R236" t="n">
+        <v>412</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>1111014112</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111014112</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>뷰티앤젤</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>0507-1339-8536</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 중부대로788번길 16 1층 뷰티앤젤</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/b_gel8536</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>0</v>
+      </c>
+      <c r="R237" t="n">
+        <v>20</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>1723741316</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1723741316</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>네일버디</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>dldei100@naver.com</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>0507-1355-2042</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 관곡로 51 가현신안아파트 상가동 1층 107호</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.buddy__?igsh=ODFnMGtrbDZjNWxm</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>1</v>
+      </c>
+      <c r="R238" t="n">
+        <v>43</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>2097386655</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2097386655</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>모두와네일</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>a0107963@naver.com</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>0507-1410-0286</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 동백죽전대로 444</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/a0107963</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>0</v>
+      </c>
+      <c r="R239" t="n">
+        <v>12</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>67002071</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/67002071</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>더뉴네일</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>0507-1398-3534</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 강남로 13 칼리지 포인트 106호</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_n.e.w_</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>12</v>
+      </c>
+      <c r="R240" t="n">
+        <v>343</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>1752738480</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1752738480</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>달꼼네일</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>070-8950-0731</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>경기도 광주시 상태길 43 1층 달꼼네일</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dalccom_nail</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>6</v>
+      </c>
+      <c r="R241" t="n">
+        <v>21</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>1227967802</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1227967802</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>르봉네일</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>lebonnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>0507-1439-4822</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 동백5로 22 B103호</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebon._.nail?igsh=MTgwNncxdGZvYTl0MA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>80</v>
+      </c>
+      <c r="R242" t="n">
+        <v>200</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>1941523558</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1941523558</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>네일테라스</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>031-263-2333</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 달맞이로 13 102동 109호</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>1</v>
+      </c>
+      <c r="R243" t="n">
+        <v>4</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>1822121186</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1822121186</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>티오네일</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>0507-1398-7541</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄반송1길 20-10 110호</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/t.o__nail</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>39</v>
+      </c>
+      <c r="R244" t="n">
+        <v>67</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>2024082852</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024082852</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>비유네일</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>0507-1342-1490</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>경기도 광주시 능평로 201 4층 402-1호(왼쪽입구)</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hanbee_u</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>0</v>
+      </c>
+      <c r="R245" t="n">
+        <v>90</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>1056632537</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1056632537</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>뮤트네일</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>0507-1388-4586</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 동백3로11번길 12 1층 119호</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mute._.nail</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>211</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>5</v>
+      </c>
+      <c r="R246" t="n">
+        <v>216</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>1796350578</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1796350578</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>제이드네일</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>jade_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>031-263-8219</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 현암로 119 죽전메디뷰 1층 107호 제이드 네일 스튜디오</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jade_nail</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>141</v>
+      </c>
+      <c r="R247" t="n">
+        <v>149</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>37592519</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37592519</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>슈네일 기흥본점</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>zzzzisoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>0507-1387-0150</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 구갈로60번길 5-1 6층 602호</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the9.beauty_giheung</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>34</v>
+      </c>
+      <c r="R248" t="n">
+        <v>222</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>1102342903</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1102342903</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>내성발톱무좀 풋풋하다</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>blessbeauty7@naver.com</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>0507-1378-3772</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 도청로18번길 26 3층 378호</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/footfoothd</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>167</v>
+      </c>
+      <c r="R249" t="n">
+        <v>417</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>1970948674</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1970948674</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>머바르니네일 기흥구청점</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>hyunjin418@naver.com</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>0507-1406-4005</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 구갈로 70 메가타운 204호 머바르니네일 기흥구청점</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hyunjin418</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>2317</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>332</v>
+      </c>
+      <c r="R250" t="n">
+        <v>2649</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>835125349</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/835125349</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>칠하고네일</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>0507-1439-3024</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 용구대로2772번길 20 1층 칠하고네일</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://instagram.com/7hago_nail?igshid=1ejajkfvxqjmf</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>16</v>
+      </c>
+      <c r="R251" t="n">
+        <v>67</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>1487704627</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1487704627</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>유니네일</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>0507-1364-6226</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 봉영로 1612 1층 130호</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yuni.nail_s2/</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>13</v>
+      </c>
+      <c r="R252" t="n">
+        <v>96</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>1460745490</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1460745490</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>쌍둥이네일</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>031-264-0707</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 성복2로 126 성복동 LG빌리지3차 단지내 상가 2층 209호</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>2</v>
+      </c>
+      <c r="R253" t="n">
+        <v>9</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>36215487</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36215487</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>네일 하로가</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>0507-1486-1992</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄신리천로4길 47 힐스테이트 동탄포레 상가 108호</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailharoga</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>1611</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>48</v>
+      </c>
+      <c r="R254" t="n">
+        <v>1659</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>1070882932</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070882932</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>네일드레스</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>0507-1392-7820</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄공원로3길 10 102호</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_dress1</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>7</v>
+      </c>
+      <c r="R255" t="n">
+        <v>143</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>1894449015</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1894449015</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>그리밍네일</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 수지로113번길 15 상가동 208, 209호</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/griming.nail</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" t="n">
+        <v>6</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>2016055278</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2016055278</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>네일은JIN</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>0507-1315-4320</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크쇼핑몰 1층 B-43</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nails__jin</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>409</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>64</v>
+      </c>
+      <c r="R257" t="n">
+        <v>473</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>1804453394</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1804453394</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>여우손톱</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>jayjayjensen@naver.com</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 중부대로1313번길 20-25 1층, 농협 역북지점 골목</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/foxnail_dahi</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>41</v>
+      </c>
+      <c r="R258" t="n">
+        <v>141</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>38290648</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38290648</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>엔더블유 네일왁싱</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>0507-1341-5437</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 반달로35번길 30 228호</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_fGZqs</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>1049</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>609</v>
+      </c>
+      <c r="R259" t="n">
+        <v>1658</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>1454353978</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1454353978</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>버던트네일</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 반달로35번길 30 3층 313호</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/verdant_nail?igsh=dGdrcmcxZXA5djA0&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>9</v>
+      </c>
+      <c r="R260" t="n">
+        <v>382</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>2082347591</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2082347591</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>연화네일</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>0507-1463-6112</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 강남동로114번길 18-11 101호</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/atelier_yeonhwa.nail</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>0</v>
+      </c>
+      <c r="R261" t="n">
+        <v>11</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>2041924922</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2041924922</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>노메이크업</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>031-335-0017</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 금령로27번길 22-22 럭스빌 상가 1층 노메이크업</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>0</v>
+      </c>
+      <c r="R262" t="n">
+        <v>1</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>2058216415</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2058216415</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>네일알</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>0507-1431-3341</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 포은대로313번길 7-10 이편한세상상가 101-1호</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>1</v>
+      </c>
+      <c r="R263" t="n">
+        <v>2</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>1923076122</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1923076122</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>샾네일</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>0507-1476-2381</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 지삼로590번길 29 4호</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shop_nail2327</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>0</v>
+      </c>
+      <c r="R264" t="n">
+        <v>9</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>1316606664</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1316606664</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>무드업네일</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 문인로17번길 6 1층</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/moodup_nail</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>9</v>
+      </c>
+      <c r="R265" t="n">
+        <v>32</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>1509008232</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1509008232</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>JYP속눈썹&amp;손톱반짝</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>good32qq@naver.com</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>0507-1390-4182</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄대로4길 47 AJ프라자 4층</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nail_4182/</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>112</v>
+      </c>
+      <c r="R266" t="n">
+        <v>163</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>1822969499</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1822969499</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>솜솜네일</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>0507-1416-2241</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로 51 포스빌 지하1층 50호 솜솜네일</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/somsomnail_</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>405</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>51</v>
+      </c>
+      <c r="R267" t="n">
+        <v>456</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>1165691375</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1165691375</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>네일 디어제이</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄순환대로 689 삼성프라자 206호</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/naildear.j_</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>937</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>8</v>
+      </c>
+      <c r="R268" t="n">
+        <v>945</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>1149998420</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1149998420</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>스페이스와이 SPACE Y</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>yonseiblog@naver.com</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>0507-1396-3851</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄대로 599 303호</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
         <is>
           <t>1315149633</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="U269" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1315149633</t>
         </is>
       </c>
-      <c r="V219" t="inlineStr">
+      <c r="V269" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_nail/용인_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/용인_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V727"/>
+  <dimension ref="A1:V753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -67221,34 +67221,30 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>함스헤어</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>rose74741@naver.com</t>
-        </is>
-      </c>
+          <t>손네일</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr">
         <is>
-          <t>0507-1374-7910</t>
+          <t>0507-1325-4489</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
       <c r="G725" t="inlineStr">
         <is>
-          <t>경기도 용인시 처인구 유림로 148-4</t>
+          <t>경기도 용인시 기흥구 죽전로15번길 3-20</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/kim_sonnail</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -67258,7 +67254,7 @@
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
@@ -67279,17 +67275,17 @@
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P725" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="Q725" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R725" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="S725" t="inlineStr">
         <is>
@@ -67298,12 +67294,12 @@
       </c>
       <c r="T725" t="inlineStr">
         <is>
-          <t>37036591</t>
+          <t>35316312</t>
         </is>
       </c>
       <c r="U725" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37036591</t>
+          <t>https://m.place.naver.com/place/35316312</t>
         </is>
       </c>
       <c r="V725" t="inlineStr">
@@ -67315,34 +67311,34 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>스페이스와이 SPACE Y</t>
+          <t>네일드로우</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>yonseiblog@naver.com</t>
+          <t>ssuna0116@naver.com</t>
         </is>
       </c>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
-          <t>0507-1396-3851</t>
+          <t>0507-1483-2243</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
       <c r="G726" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로 599 303호</t>
+          <t>경기도 용인시 기흥구 중부대로 184 힉스유타워 상가동 1층 169-2호</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_draw_jin</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -67352,7 +67348,7 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
@@ -67368,22 +67364,22 @@
       <c r="M726" t="inlineStr"/>
       <c r="N726" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P726" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q726" t="n">
         <v>0</v>
       </c>
       <c r="R726" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S726" t="inlineStr">
         <is>
@@ -67392,12 +67388,12 @@
       </c>
       <c r="T726" t="inlineStr">
         <is>
-          <t>1315149633</t>
+          <t>1439291395</t>
         </is>
       </c>
       <c r="U726" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315149633</t>
+          <t>https://m.place.naver.com/place/1439291395</t>
         </is>
       </c>
       <c r="V726" t="inlineStr">
@@ -67409,26 +67405,30 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>웰디자인</t>
+          <t>네일리르</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr"/>
-      <c r="E727" t="inlineStr"/>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>0507-1469-2295</t>
+        </is>
+      </c>
       <c r="F727" t="inlineStr"/>
       <c r="G727" t="inlineStr">
         <is>
-          <t>경기도 용인시 수지구 풍덕천로 52</t>
+          <t>경기도 용인시 기흥구 죽전로 23 2층 202호</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/well_design24</t>
+          <t>https://www.instagram.com/nail_rire_</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -67463,30 +67463,2438 @@
         </is>
       </c>
       <c r="P727" t="n">
+        <v>376</v>
+      </c>
+      <c r="Q727" t="n">
+        <v>19</v>
+      </c>
+      <c r="R727" t="n">
+        <v>395</v>
+      </c>
+      <c r="S727" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T727" t="inlineStr">
+        <is>
+          <t>1370128010</t>
+        </is>
+      </c>
+      <c r="U727" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370128010</t>
+        </is>
+      </c>
+      <c r="V727" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>에이치네일</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>remon103@naver.com</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr"/>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>0507-1318-3991</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr"/>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄대로5길 15 5층 5026호</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr"/>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P728" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q728" t="n">
         <v>1</v>
       </c>
-      <c r="Q727" t="n">
+      <c r="R728" t="n">
+        <v>14</v>
+      </c>
+      <c r="S728" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T728" t="inlineStr">
+        <is>
+          <t>2017869489</t>
+        </is>
+      </c>
+      <c r="U728" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2017869489</t>
+        </is>
+      </c>
+      <c r="V728" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>뮤제네일 수원영통점</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>sarsh1205@naver.com</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr"/>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>0507-1389-8681</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr"/>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 덕영대로 1699 303A호</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/musee_nail?igsh=MTk1aDdqYTdiaGt5cA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr"/>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P729" t="n">
+        <v>286</v>
+      </c>
+      <c r="Q729" t="n">
+        <v>50</v>
+      </c>
+      <c r="R729" t="n">
+        <v>336</v>
+      </c>
+      <c r="S729" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T729" t="inlineStr">
+        <is>
+          <t>2045620652</t>
+        </is>
+      </c>
+      <c r="U729" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2045620652</t>
+        </is>
+      </c>
+      <c r="V729" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>네일가든</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>minee_94@naver.com</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr"/>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>031-896-4141</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr"/>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 현암로 153 건영타운 1층</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr"/>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P730" t="n">
         <v>0</v>
       </c>
-      <c r="R727" t="n">
+      <c r="Q730" t="n">
+        <v>0</v>
+      </c>
+      <c r="R730" t="n">
+        <v>0</v>
+      </c>
+      <c r="S730" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T730" t="inlineStr">
+        <is>
+          <t>34762150</t>
+        </is>
+      </c>
+      <c r="U730" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34762150</t>
+        </is>
+      </c>
+      <c r="V730" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>네일쥬르</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>laumi22@naver.com</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr"/>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>0507-1468-2788</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr"/>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 현암로 148 스카이프라자 3층 302호</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailjours/</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr"/>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P731" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q731" t="n">
+        <v>8</v>
+      </c>
+      <c r="R731" t="n">
+        <v>254</v>
+      </c>
+      <c r="S731" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T731" t="inlineStr">
+        <is>
+          <t>1186917891</t>
+        </is>
+      </c>
+      <c r="U731" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1186917891</t>
+        </is>
+      </c>
+      <c r="V731" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>에이네일</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr"/>
+      <c r="D732" t="inlineStr"/>
+      <c r="E732" t="inlineStr"/>
+      <c r="F732" t="inlineStr"/>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 남사읍 한숲로 45 B동 4층 417호</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.nail_hansoop</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr"/>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P732" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q732" t="n">
+        <v>0</v>
+      </c>
+      <c r="R732" t="n">
+        <v>47</v>
+      </c>
+      <c r="S732" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T732" t="inlineStr">
+        <is>
+          <t>1604007860</t>
+        </is>
+      </c>
+      <c r="U732" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1604007860</t>
+        </is>
+      </c>
+      <c r="V732" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>더와이네일</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>msbhaha@naver.com</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr"/>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>0507-1418-0427</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr"/>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 명지로 24 the럭스나인 204로 더와이네일</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>http://instagram.com/the_y_nail_</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr"/>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P733" t="n">
+        <v>424</v>
+      </c>
+      <c r="Q733" t="n">
+        <v>7</v>
+      </c>
+      <c r="R733" t="n">
+        <v>431</v>
+      </c>
+      <c r="S733" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T733" t="inlineStr">
+        <is>
+          <t>1853278359</t>
+        </is>
+      </c>
+      <c r="U733" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853278359</t>
+        </is>
+      </c>
+      <c r="V733" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>샤네일</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>jgy5220@naver.com</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr"/>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>0507-1314-1643</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr"/>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 금학로 442</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>http://instagram.com/cha.nail__</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr"/>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P734" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q734" t="n">
+        <v>10</v>
+      </c>
+      <c r="R734" t="n">
+        <v>47</v>
+      </c>
+      <c r="S734" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T734" t="inlineStr">
+        <is>
+          <t>1311854053</t>
+        </is>
+      </c>
+      <c r="U734" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1311854053</t>
+        </is>
+      </c>
+      <c r="V734" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>네일도</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>sungunara226@naver.com</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr"/>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>0507-1359-5645</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr"/>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 광교마을로 54 광교 SB타운 307호</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__nail.do__?igsh=MWZmMm9kYzY0bDYxdA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr"/>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P735" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q735" t="n">
+        <v>6</v>
+      </c>
+      <c r="R735" t="n">
+        <v>46</v>
+      </c>
+      <c r="S735" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T735" t="inlineStr">
+        <is>
+          <t>2034335729</t>
+        </is>
+      </c>
+      <c r="U735" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2034335729</t>
+        </is>
+      </c>
+      <c r="V735" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>레푸스 수지구청점</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>aden727@naver.com</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr"/>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>0507-1439-3384</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr"/>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 풍덕천로 122 4층 405-2호</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aden727</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr"/>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P736" t="n">
+        <v>1117</v>
+      </c>
+      <c r="Q736" t="n">
+        <v>903</v>
+      </c>
+      <c r="R736" t="n">
+        <v>2020</v>
+      </c>
+      <c r="S736" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T736" t="inlineStr">
+        <is>
+          <t>1846095043</t>
+        </is>
+      </c>
+      <c r="U736" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1846095043</t>
+        </is>
+      </c>
+      <c r="V736" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>네일엘로이 동탄</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>gu17190@naver.com</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr"/>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>0507-1310-1386</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr"/>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄공원로3길 32-6 1층 103호</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_elroy</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr"/>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P737" t="n">
+        <v>278</v>
+      </c>
+      <c r="Q737" t="n">
+        <v>115</v>
+      </c>
+      <c r="R737" t="n">
+        <v>393</v>
+      </c>
+      <c r="S737" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T737" t="inlineStr">
+        <is>
+          <t>1881753815</t>
+        </is>
+      </c>
+      <c r="U737" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1881753815</t>
+        </is>
+      </c>
+      <c r="V737" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>리네일</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr"/>
+      <c r="D738" t="inlineStr"/>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>0507-1348-9626</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr"/>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 정평로 40-1 거묵상가1 2층 201호</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xjZtqG</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr"/>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P738" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q738" t="n">
+        <v>0</v>
+      </c>
+      <c r="R738" t="n">
+        <v>24</v>
+      </c>
+      <c r="S738" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T738" t="inlineStr">
+        <is>
+          <t>1613647201</t>
+        </is>
+      </c>
+      <c r="U738" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1613647201</t>
+        </is>
+      </c>
+      <c r="V738" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>꾸밈헤어&amp;네일</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>aengtori@naver.com</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr"/>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>031-335-1259</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr"/>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 포곡읍 둔전로65번길 11 1층 안쪽 상가 꾸밈헤어&amp;네일</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_LdMsxb</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr"/>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P739" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q739" t="n">
+        <v>0</v>
+      </c>
+      <c r="R739" t="n">
+        <v>17</v>
+      </c>
+      <c r="S739" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T739" t="inlineStr">
+        <is>
+          <t>1003645633</t>
+        </is>
+      </c>
+      <c r="U739" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1003645633</t>
+        </is>
+      </c>
+      <c r="V739" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>혠즈네일</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>naeun1210@naver.com</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr"/>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>0507-1496-7951</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr"/>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 흥덕2로65번길 12-9 1층 혠즈네일</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>http://instagram.com/hyenznail</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr"/>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P740" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q740" t="n">
+        <v>6</v>
+      </c>
+      <c r="R740" t="n">
+        <v>286</v>
+      </c>
+      <c r="S740" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T740" t="inlineStr">
+        <is>
+          <t>1967281250</t>
+        </is>
+      </c>
+      <c r="U740" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1967281250</t>
+        </is>
+      </c>
+      <c r="V740" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>네일드벨</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr"/>
+      <c r="D741" t="inlineStr"/>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>0507-1378-1596</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr"/>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 반달로7번길 40 2층 223-1호</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.de_belle?igsh=cHNjdHAzcG9qaDho&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr"/>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P741" t="n">
+        <v>261</v>
+      </c>
+      <c r="Q741" t="n">
+        <v>6</v>
+      </c>
+      <c r="R741" t="n">
+        <v>267</v>
+      </c>
+      <c r="S741" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T741" t="inlineStr">
+        <is>
+          <t>1129106136</t>
+        </is>
+      </c>
+      <c r="U741" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1129106136</t>
+        </is>
+      </c>
+      <c r="V741" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>제이뷰티</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>j_beauty_lab@naver.com</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr"/>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>0507-1319-1271</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr"/>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 한터로 159 1층 103호</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imjeongyun187?igsh=MWh6bmZ6enV1Ynk1aA==</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr"/>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P742" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q742" t="n">
+        <v>17</v>
+      </c>
+      <c r="R742" t="n">
+        <v>217</v>
+      </c>
+      <c r="S742" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T742" t="inlineStr">
+        <is>
+          <t>1883484078</t>
+        </is>
+      </c>
+      <c r="U742" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1883484078</t>
+        </is>
+      </c>
+      <c r="V742" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>네일마주봄</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>prim-rose@naver.com</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr"/>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>0507-1361-5110</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr"/>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 백옥대로 1130-1 1층 네일마주봄</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Bxexnbxb</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr"/>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P743" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q743" t="n">
+        <v>54</v>
+      </c>
+      <c r="R743" t="n">
+        <v>131</v>
+      </c>
+      <c r="S743" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T743" t="inlineStr">
+        <is>
+          <t>1778117192</t>
+        </is>
+      </c>
+      <c r="U743" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1778117192</t>
+        </is>
+      </c>
+      <c r="V743" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Wnail</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>silverg0210@naver.com</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr"/>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>0507-1378-5660</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr"/>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 광교중앙로295번길 25 a동 103호 w nail</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/w_nail4940</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr"/>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P744" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q744" t="n">
+        <v>2</v>
+      </c>
+      <c r="R744" t="n">
+        <v>193</v>
+      </c>
+      <c r="S744" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T744" t="inlineStr">
+        <is>
+          <t>1317247038</t>
+        </is>
+      </c>
+      <c r="U744" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1317247038</t>
+        </is>
+      </c>
+      <c r="V744" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>쁘네일래쉬</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>cptai3@naver.com</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr"/>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>0507-1370-1593</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 영통로331번길 70 1층</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_wGLgxj</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr"/>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P745" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q745" t="n">
+        <v>48</v>
+      </c>
+      <c r="R745" t="n">
+        <v>156</v>
+      </c>
+      <c r="S745" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T745" t="inlineStr">
+        <is>
+          <t>1734795951</t>
+        </is>
+      </c>
+      <c r="U745" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1734795951</t>
+        </is>
+      </c>
+      <c r="V745" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>희연네일 광교중앙역점</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>heeyeoun_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr"/>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="inlineStr"/>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 도청로18번길 26 1동 지하2층 B258호</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>https://http//pf.kakao.com/_YGkxgG</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr"/>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P746" t="n">
+        <v>406</v>
+      </c>
+      <c r="Q746" t="n">
+        <v>71</v>
+      </c>
+      <c r="R746" t="n">
+        <v>477</v>
+      </c>
+      <c r="S746" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T746" t="inlineStr">
+        <is>
+          <t>1710940821</t>
+        </is>
+      </c>
+      <c r="U746" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1710940821</t>
+        </is>
+      </c>
+      <c r="V746" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>41.네일</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>jhu5239@naver.com</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>031-266-4141</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr"/>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 성복2로 17 골드프라자 1층 41.nail</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>http://instagram.com/41.nail</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr"/>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P747" t="n">
+        <v>420</v>
+      </c>
+      <c r="Q747" t="n">
+        <v>16</v>
+      </c>
+      <c r="R747" t="n">
+        <v>436</v>
+      </c>
+      <c r="S747" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T747" t="inlineStr">
+        <is>
+          <t>1052711620</t>
+        </is>
+      </c>
+      <c r="U747" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1052711620</t>
+        </is>
+      </c>
+      <c r="V747" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>네일손발공주 보정점</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>miri3891@naver.com</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr"/>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>0507-1437-1469</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr"/>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 죽현로 8-20 아이원프라자 1층 네일손발공주</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_s.b.princess</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr"/>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P748" t="n">
+        <v>511</v>
+      </c>
+      <c r="Q748" t="n">
+        <v>15</v>
+      </c>
+      <c r="R748" t="n">
+        <v>526</v>
+      </c>
+      <c r="S748" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T748" t="inlineStr">
+        <is>
+          <t>1798087647</t>
+        </is>
+      </c>
+      <c r="U748" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1798087647</t>
+        </is>
+      </c>
+      <c r="V748" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>네일앤코</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr"/>
+      <c r="D749" t="inlineStr"/>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>070-5100-0616</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 센트럴파크로127번길 131-3 1층 101호</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail._.ko?igsh=OGwweW53NnNtNnl6&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr"/>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P749" t="n">
+        <v>327</v>
+      </c>
+      <c r="Q749" t="n">
+        <v>6</v>
+      </c>
+      <c r="R749" t="n">
+        <v>333</v>
+      </c>
+      <c r="S749" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T749" t="inlineStr">
+        <is>
+          <t>1872894083</t>
+        </is>
+      </c>
+      <c r="U749" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1872894083</t>
+        </is>
+      </c>
+      <c r="V749" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>온앤온네일</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>kimjieun514@naver.com</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr"/>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄순환대로 263 1층 111호</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/on.on_nail</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr"/>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P750" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q750" t="n">
+        <v>88</v>
+      </c>
+      <c r="R750" t="n">
+        <v>360</v>
+      </c>
+      <c r="S750" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T750" t="inlineStr">
+        <is>
+          <t>1997573833</t>
+        </is>
+      </c>
+      <c r="U750" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1997573833</t>
+        </is>
+      </c>
+      <c r="V750" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>함스헤어</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>rose74741@naver.com</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr"/>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>0507-1374-7910</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr"/>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>경기도 용인시 처인구 유림로 148-4</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr"/>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P751" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q751" t="n">
+        <v>0</v>
+      </c>
+      <c r="R751" t="n">
+        <v>37</v>
+      </c>
+      <c r="S751" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T751" t="inlineStr">
+        <is>
+          <t>37036591</t>
+        </is>
+      </c>
+      <c r="U751" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37036591</t>
+        </is>
+      </c>
+      <c r="V751" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>스페이스와이 SPACE Y</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>yonseiblog@naver.com</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr"/>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>0507-1396-3851</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr"/>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄대로 599 303호</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr"/>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P752" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q752" t="n">
+        <v>0</v>
+      </c>
+      <c r="R752" t="n">
+        <v>0</v>
+      </c>
+      <c r="S752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T752" t="inlineStr">
+        <is>
+          <t>1315149633</t>
+        </is>
+      </c>
+      <c r="U752" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1315149633</t>
+        </is>
+      </c>
+      <c r="V752" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>웰디자인</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr"/>
+      <c r="D753" t="inlineStr"/>
+      <c r="E753" t="inlineStr"/>
+      <c r="F753" t="inlineStr"/>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>경기도 용인시 수지구 풍덕천로 52</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/well_design24</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr"/>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P753" t="n">
         <v>1</v>
       </c>
-      <c r="S727" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T727" t="inlineStr">
+      <c r="Q753" t="n">
+        <v>0</v>
+      </c>
+      <c r="R753" t="n">
+        <v>1</v>
+      </c>
+      <c r="S753" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T753" t="inlineStr">
         <is>
           <t>1956094235</t>
         </is>
       </c>
-      <c r="U727" t="inlineStr">
+      <c r="U753" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1956094235</t>
         </is>
       </c>
-      <c r="V727" t="inlineStr">
+      <c r="V753" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
